--- a/I Отчет ПРОДАЖИ 10.2026.xlsx
+++ b/I Отчет ПРОДАЖИ 10.2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3397"/>
+  <dimension ref="A1:E3414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65384,62 +65384,441 @@
     <row r="3395">
       <c r="A3395" t="inlineStr">
         <is>
+          <t>Аллазова Телли</t>
+        </is>
+      </c>
+      <c r="B3395" t="inlineStr">
+        <is>
+          <t>Б* Хлеб Тосканский</t>
+        </is>
+      </c>
+      <c r="C3395" t="inlineStr">
+        <is>
+          <t>Выручка расходной накладной</t>
+        </is>
+      </c>
+      <c r="D3395" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E3395" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="3396">
+      <c r="A3396" t="inlineStr">
+        <is>
+          <t>Альжанова Зауреш</t>
+        </is>
+      </c>
+      <c r="B3396" t="inlineStr">
+        <is>
+          <t>Б* Сочники с творогом (1шт)</t>
+        </is>
+      </c>
+      <c r="C3396" t="inlineStr">
+        <is>
+          <t>Выручка расходной накладной</t>
+        </is>
+      </c>
+      <c r="D3396" t="n">
+        <v>-10</v>
+      </c>
+      <c r="E3396" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="3397">
+      <c r="A3397" t="inlineStr">
+        <is>
+          <t>Бейсембаева Галия</t>
+        </is>
+      </c>
+      <c r="B3397" t="inlineStr">
+        <is>
+          <t>Б* Хлеб Тосканский</t>
+        </is>
+      </c>
+      <c r="C3397" t="inlineStr">
+        <is>
+          <t>Выручка расходной накладной</t>
+        </is>
+      </c>
+      <c r="D3397" t="n">
+        <v>-17</v>
+      </c>
+      <c r="E3397" t="n">
+        <v>2805</v>
+      </c>
+    </row>
+    <row r="3398">
+      <c r="A3398" t="inlineStr"/>
+      <c r="B3398" t="inlineStr">
+        <is>
+          <t>Б* Хлеб сливочный французский (1шт)</t>
+        </is>
+      </c>
+      <c r="C3398" t="inlineStr">
+        <is>
+          <t>Выручка расходной накладной</t>
+        </is>
+      </c>
+      <c r="D3398" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E3398" t="n">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="3399">
+      <c r="A3399" t="inlineStr">
+        <is>
+          <t>Билисбекова Жумагуль</t>
+        </is>
+      </c>
+      <c r="B3399" t="inlineStr">
+        <is>
+          <t>Б* Сочники с творогом (1шт)</t>
+        </is>
+      </c>
+      <c r="C3399" t="inlineStr">
+        <is>
+          <t>Выручка расходной накладной</t>
+        </is>
+      </c>
+      <c r="D3399" t="n">
+        <v>-10</v>
+      </c>
+      <c r="E3399" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="3400">
+      <c r="A3400" t="inlineStr"/>
+      <c r="B3400" t="inlineStr">
+        <is>
+          <t>Б* Хлеб Тосканский</t>
+        </is>
+      </c>
+      <c r="C3400" t="inlineStr">
+        <is>
+          <t>Выручка расходной накладной</t>
+        </is>
+      </c>
+      <c r="D3400" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E3400" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3401">
+      <c r="A3401" t="inlineStr">
+        <is>
+          <t>Дубинина Нина</t>
+        </is>
+      </c>
+      <c r="B3401" t="inlineStr">
+        <is>
+          <t>Б* Хлеб Тосканский</t>
+        </is>
+      </c>
+      <c r="C3401" t="inlineStr">
+        <is>
+          <t>Выручка расходной накладной</t>
+        </is>
+      </c>
+      <c r="D3401" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E3401" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3402">
+      <c r="A3402" t="inlineStr">
+        <is>
+          <t>Изгибаев Медетбек</t>
+        </is>
+      </c>
+      <c r="B3402" t="inlineStr">
+        <is>
+          <t>Б* Хлеб Тосканский</t>
+        </is>
+      </c>
+      <c r="C3402" t="inlineStr">
+        <is>
+          <t>Выручка расходной накладной</t>
+        </is>
+      </c>
+      <c r="D3402" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E3402" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="3403">
+      <c r="A3403" t="inlineStr">
+        <is>
           <t>Иналка Фуд Сервис ТОО</t>
         </is>
       </c>
-      <c r="B3395" t="inlineStr">
+      <c r="B3403" t="inlineStr">
         <is>
           <t>Упак Маффин шоколадный (24шт)</t>
         </is>
       </c>
-      <c r="C3395" t="inlineStr">
-        <is>
-          <t>Выручка расходной накладной</t>
-        </is>
-      </c>
-      <c r="D3395" t="n">
+      <c r="C3403" t="inlineStr">
+        <is>
+          <t>Выручка расходной накладной</t>
+        </is>
+      </c>
+      <c r="D3403" t="n">
         <v>-15</v>
       </c>
-      <c r="E3395" t="n">
+      <c r="E3403" t="n">
         <v>108000</v>
       </c>
     </row>
-    <row r="3396">
-      <c r="A3396" t="inlineStr"/>
-      <c r="B3396" t="inlineStr">
+    <row r="3404">
+      <c r="A3404" t="inlineStr"/>
+      <c r="B3404" t="inlineStr">
         <is>
           <t>Упак Самса с курицей готов ФЗ СМ (30шт гофра )</t>
         </is>
       </c>
-      <c r="C3396" t="inlineStr">
-        <is>
-          <t>Выручка расходной накладной</t>
-        </is>
-      </c>
-      <c r="D3396" t="n">
+      <c r="C3404" t="inlineStr">
+        <is>
+          <t>Выручка расходной накладной</t>
+        </is>
+      </c>
+      <c r="D3404" t="n">
         <v>-3</v>
       </c>
-      <c r="E3396" t="n">
+      <c r="E3404" t="n">
         <v>20250</v>
       </c>
     </row>
-    <row r="3397">
-      <c r="A3397" t="inlineStr"/>
-      <c r="B3397" t="inlineStr">
+    <row r="3405">
+      <c r="A3405" t="inlineStr"/>
+      <c r="B3405" t="inlineStr">
         <is>
           <t>Упак Сырники творожные лоток (20шт)</t>
         </is>
       </c>
-      <c r="C3397" t="inlineStr">
-        <is>
-          <t>Выручка расходной накладной</t>
-        </is>
-      </c>
-      <c r="D3397" t="n">
+      <c r="C3405" t="inlineStr">
+        <is>
+          <t>Выручка расходной накладной</t>
+        </is>
+      </c>
+      <c r="D3405" t="n">
         <v>-15</v>
       </c>
-      <c r="E3397" t="n">
+      <c r="E3405" t="n">
         <v>81000</v>
+      </c>
+    </row>
+    <row r="3406">
+      <c r="A3406" t="inlineStr">
+        <is>
+          <t>Калиева Бакыт</t>
+        </is>
+      </c>
+      <c r="B3406" t="inlineStr">
+        <is>
+          <t>Б* Хлеб Тосканский</t>
+        </is>
+      </c>
+      <c r="C3406" t="inlineStr">
+        <is>
+          <t>Выручка расходной накладной</t>
+        </is>
+      </c>
+      <c r="D3406" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E3406" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="3407">
+      <c r="A3407" t="inlineStr">
+        <is>
+          <t>Калмурзаева Гулсауир</t>
+        </is>
+      </c>
+      <c r="B3407" t="inlineStr">
+        <is>
+          <t>Б* Сочники с творогом (1шт)</t>
+        </is>
+      </c>
+      <c r="C3407" t="inlineStr">
+        <is>
+          <t>Выручка расходной накладной</t>
+        </is>
+      </c>
+      <c r="D3407" t="n">
+        <v>-20</v>
+      </c>
+      <c r="E3407" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="3408">
+      <c r="A3408" t="inlineStr">
+        <is>
+          <t>Куанышбек Гулдераим</t>
+        </is>
+      </c>
+      <c r="B3408" t="inlineStr">
+        <is>
+          <t>Б* Хлеб Тосканский</t>
+        </is>
+      </c>
+      <c r="C3408" t="inlineStr">
+        <is>
+          <t>Выручка расходной накладной</t>
+        </is>
+      </c>
+      <c r="D3408" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E3408" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="3409">
+      <c r="A3409" t="inlineStr">
+        <is>
+          <t>Кузенова Мария</t>
+        </is>
+      </c>
+      <c r="B3409" t="inlineStr">
+        <is>
+          <t>Б* Хлеб сливочный французский (1шт)</t>
+        </is>
+      </c>
+      <c r="C3409" t="inlineStr">
+        <is>
+          <t>Выручка расходной накладной</t>
+        </is>
+      </c>
+      <c r="D3409" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E3409" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="3410">
+      <c r="A3410" t="inlineStr">
+        <is>
+          <t>Култаева Жадыра</t>
+        </is>
+      </c>
+      <c r="B3410" t="inlineStr">
+        <is>
+          <t>Б* Хлеб Тосканский</t>
+        </is>
+      </c>
+      <c r="C3410" t="inlineStr">
+        <is>
+          <t>Выручка расходной накладной</t>
+        </is>
+      </c>
+      <c r="D3410" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E3410" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="3411">
+      <c r="A3411" t="inlineStr">
+        <is>
+          <t>Мамбетаев Оралгалы</t>
+        </is>
+      </c>
+      <c r="B3411" t="inlineStr">
+        <is>
+          <t>Б* Хлеб сливочный французский (1шт)</t>
+        </is>
+      </c>
+      <c r="C3411" t="inlineStr">
+        <is>
+          <t>Выручка расходной накладной</t>
+        </is>
+      </c>
+      <c r="D3411" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E3411" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="3412">
+      <c r="A3412" t="inlineStr">
+        <is>
+          <t>Мухтарова Арайлым</t>
+        </is>
+      </c>
+      <c r="B3412" t="inlineStr">
+        <is>
+          <t>Б* Хлеб Тосканский</t>
+        </is>
+      </c>
+      <c r="C3412" t="inlineStr">
+        <is>
+          <t>Выручка расходной накладной</t>
+        </is>
+      </c>
+      <c r="D3412" t="n">
+        <v>-10</v>
+      </c>
+      <c r="E3412" t="n">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="3413">
+      <c r="A3413" t="inlineStr"/>
+      <c r="B3413" t="inlineStr">
+        <is>
+          <t>Б* Хлеб сливочный французский (1шт)</t>
+        </is>
+      </c>
+      <c r="C3413" t="inlineStr">
+        <is>
+          <t>Выручка расходной накладной</t>
+        </is>
+      </c>
+      <c r="D3413" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E3413" t="n">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="3414">
+      <c r="A3414" t="inlineStr">
+        <is>
+          <t>Нугымбетова Дана</t>
+        </is>
+      </c>
+      <c r="B3414" t="inlineStr">
+        <is>
+          <t>Б* Хлеб Тосканский</t>
+        </is>
+      </c>
+      <c r="C3414" t="inlineStr">
+        <is>
+          <t>Выручка расходной накладной</t>
+        </is>
+      </c>
+      <c r="D3414" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E3414" t="n">
+        <v>330</v>
       </c>
     </row>
   </sheetData>

--- a/I Отчет ПРОДАЖИ 10.2026.xlsx
+++ b/I Отчет ПРОДАЖИ 10.2026.xlsx
@@ -37693,10 +37693,10 @@
         </is>
       </c>
       <c r="D1956" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="E1956" t="n">
-        <v>4140</v>
+        <v>3450</v>
       </c>
     </row>
     <row r="1957">
@@ -44322,10 +44322,10 @@
         </is>
       </c>
       <c r="D2303" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="E2303" t="n">
-        <v>2646</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="2304">
